--- a/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D84" authorId="0">
+    <comment ref="C82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -49,27 +49,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="196">
-  <si>
-    <t>#</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="199">
+  <si>
+    <t>##var</t>
   </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Des</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>测试说明</t>
   </si>
   <si>
     <t>值</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>初始化任务</t>
@@ -1685,1584 +1694,1590 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G143"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:F141"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="89.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="89.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.5" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="4:4">
-      <c r="D2" s="1" t="s">
+    <row r="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:7">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7">
+        <v>100001</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
+        <v>600000111</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:7">
-      <c r="C4" s="5" t="s">
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B8" s="8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B10" s="8">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B11" s="8">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B12" s="1">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B13" s="1">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B15" s="1">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B16" s="1">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B17" s="1">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B18" s="1">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B19" s="1">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B20" s="1">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="1">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B21" s="1">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B22" s="1">
+        <v>19</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B23" s="1">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="1">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B24" s="1">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B25" s="1">
+        <v>22</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B26" s="1">
+        <v>23</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B27" s="1">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B28" s="1">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B29" s="1">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B30" s="1">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B31" s="1">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B32" s="1">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B33" s="1">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B34" s="1">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B35" s="1">
+        <v>33</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B36" s="1">
+        <v>34</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B37" s="1">
+        <v>35</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="1">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="38" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B38" s="1">
+        <v>36</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="1">
+        <v>259200</v>
+      </c>
+    </row>
+    <row r="39" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B39" s="1">
+        <v>37</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="40" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B40" s="1">
+        <v>38</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B41" s="1">
+        <v>39</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B42" s="1">
+        <v>40</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B43" s="1">
+        <v>41</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B44" s="1">
+        <v>42</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B45" s="1">
+        <v>43</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B46" s="1">
+        <v>44</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B47" s="1">
+        <v>45</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B48" s="1">
+        <v>46</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B49" s="1">
+        <v>47</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B50" s="1">
+        <v>48</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B51" s="1">
+        <v>49</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B52" s="1">
+        <v>50</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B53" s="1">
+        <v>51</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B54" s="1">
+        <v>52</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B55" s="1">
+        <v>53</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B56" s="1">
+        <v>54</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B57" s="1">
+        <v>55</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" s="1">
+        <v>20000001</v>
+      </c>
+    </row>
+    <row r="58" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B58" s="1">
+        <v>56</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B59" s="1">
+        <v>57</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B60" s="1">
+        <v>58</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B61" s="1">
+        <v>59</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B62" s="1">
+        <v>60</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D62" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B63" s="1">
+        <v>61</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B64" s="1">
+        <v>62</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B65" s="1">
+        <v>63</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B66" s="1">
+        <v>64</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66" s="1">
+        <v>30000001</v>
+      </c>
+    </row>
+    <row r="67" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B67" s="1">
+        <v>65</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B68" s="1">
+        <v>66</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B69" s="1">
+        <v>67</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B70" s="1">
+        <v>68</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="7">
+        <v>60500101</v>
+      </c>
+    </row>
+    <row r="71" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B71" s="1">
+        <v>69</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D71" s="7">
+        <v>60500201</v>
+      </c>
+    </row>
+    <row r="72" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B72" s="1">
+        <v>70</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="73" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B73" s="1">
+        <v>71</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B74" s="1">
+        <v>72</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B75" s="1">
+        <v>73</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D75" s="1">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B76" s="1">
+        <v>74</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D76" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B77" s="1">
+        <v>75</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D77" s="1">
+        <v>601502001</v>
+      </c>
+    </row>
+    <row r="78" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B78" s="1">
+        <v>76</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D78" s="1">
+        <v>40000001</v>
+      </c>
+    </row>
+    <row r="79" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B79" s="1">
+        <v>77</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="1">
+        <v>601503011</v>
+      </c>
+    </row>
+    <row r="80" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B80" s="1">
+        <v>78</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B81" s="1">
+        <v>79</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B82" s="1">
+        <v>80</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B83" s="1">
+        <v>81</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D83" s="7">
+        <v>60303101</v>
+      </c>
+    </row>
+    <row r="84" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B84" s="1">
+        <v>82</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="85" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B85" s="1">
+        <v>83</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="86" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B86" s="1">
+        <v>84</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B87" s="1">
+        <v>85</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B88" s="1">
+        <v>86</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="89" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B89" s="1">
+        <v>87</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B90" s="1">
+        <v>88</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="91" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B91" s="1">
+        <v>89</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" s="1">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="92" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B92" s="1">
+        <v>90</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="1">
+        <v>10000158</v>
+      </c>
+    </row>
+    <row r="93" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B93" s="1">
+        <v>91</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B94" s="1">
+        <v>92</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B95" s="1">
+        <v>93</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D95" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B96" s="1">
+        <v>94</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D96" s="1">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="97" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B97" s="1">
+        <v>95</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D97" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="98" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B98" s="1">
+        <v>96</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="99" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B99" s="1">
+        <v>97</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="100" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B100" s="1">
+        <v>98</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D100" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="101" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B101" s="1">
+        <v>99</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D101" s="1">
+        <v>61300001</v>
+      </c>
+    </row>
+    <row r="102" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B102" s="1">
+        <v>100</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="103" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B103" s="1">
+        <v>101</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B104" s="1">
+        <v>102</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="105" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B105" s="1">
+        <v>103</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D105" s="1">
+        <v>70000001</v>
+      </c>
+    </row>
+    <row r="106" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B106" s="1">
+        <v>104</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D106" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="107" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B107" s="1">
+        <v>105</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D107" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B108" s="1">
+        <v>106</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D108" s="1">
+        <v>80000001</v>
+      </c>
+    </row>
+    <row r="109" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B109" s="1">
+        <v>107</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B110" s="1">
+        <v>108</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D110" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B111" s="1">
+        <v>109</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D111" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:7">
-      <c r="C5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="7">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1">
-        <v>600000111</v>
-      </c>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C10" s="8">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C12" s="8">
-        <v>7</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C13" s="8">
-        <v>8</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="1">
+    </row>
+    <row r="112" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B112" s="1">
+        <v>110</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C21" s="1">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C22" s="1">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="1">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C23" s="1">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C24" s="1">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C25" s="1">
-        <v>20</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="1">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C30" s="1">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="1">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C32" s="1">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C33" s="1">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C34" s="1">
-        <v>29</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C35" s="1">
-        <v>30</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C36" s="1">
-        <v>31</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C37" s="1">
-        <v>33</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C38" s="1">
-        <v>34</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C39" s="1">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" s="1">
-        <v>86400</v>
-      </c>
-    </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C40" s="1">
-        <v>36</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E40" s="1">
-        <v>259200</v>
-      </c>
-    </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C41" s="1">
-        <v>37</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C42" s="1">
-        <v>38</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C43" s="1">
-        <v>39</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C44" s="1">
-        <v>40</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C45" s="1">
-        <v>41</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="1">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C46" s="1">
-        <v>42</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C47" s="1">
-        <v>43</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C48" s="1">
-        <v>44</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C49" s="1">
-        <v>45</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="50" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C50" s="1">
-        <v>46</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="51" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C51" s="1">
-        <v>47</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" s="1">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C52" s="1">
-        <v>48</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C53" s="1">
-        <v>49</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C54" s="1">
-        <v>50</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C55" s="1">
-        <v>51</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C56" s="1">
-        <v>52</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C57" s="1">
-        <v>53</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C58" s="1">
-        <v>54</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C59" s="1">
-        <v>55</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E59" s="1">
-        <v>20000001</v>
-      </c>
-    </row>
-    <row r="60" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C60" s="1">
-        <v>56</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C61" s="1">
-        <v>57</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C62" s="1">
-        <v>58</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E62" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C63" s="1">
-        <v>59</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C64" s="1">
-        <v>60</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E64" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C65" s="1">
-        <v>61</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C66" s="1">
-        <v>62</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C67" s="1">
-        <v>63</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C68" s="1">
-        <v>64</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E68" s="1">
-        <v>30000001</v>
-      </c>
-    </row>
-    <row r="69" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C69" s="1">
-        <v>65</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="70" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C70" s="1">
-        <v>66</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C71" s="1">
-        <v>67</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="72" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C72" s="1">
-        <v>68</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E72" s="7">
-        <v>60500101</v>
-      </c>
-    </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C73" s="1">
-        <v>69</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E73" s="7">
-        <v>60500201</v>
-      </c>
-    </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C74" s="1">
-        <v>70</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="75" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C75" s="1">
-        <v>71</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="76" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C76" s="1">
-        <v>72</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E76" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="77" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C77" s="1">
-        <v>73</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E77" s="1">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C78" s="1">
-        <v>74</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="D112" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="113" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B113" s="1">
         <v>111</v>
       </c>
-      <c r="E78" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C79" s="1">
-        <v>75</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="114" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B114" s="1">
         <v>112</v>
       </c>
-      <c r="E79" s="1">
-        <v>601502001</v>
-      </c>
-    </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C80" s="1">
-        <v>76</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E80" s="1">
-        <v>40000001</v>
-      </c>
-    </row>
-    <row r="81" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C81" s="1">
-        <v>77</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" s="1">
-        <v>601503011</v>
-      </c>
-    </row>
-    <row r="82" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C82" s="1">
-        <v>78</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E82" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C83" s="1">
-        <v>79</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C84" s="1">
-        <v>80</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C85" s="1">
-        <v>81</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E85" s="7">
-        <v>60303101</v>
-      </c>
-    </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C86" s="1">
-        <v>82</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C87" s="1">
-        <v>83</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C88" s="1">
-        <v>84</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C89" s="1">
-        <v>85</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C90" s="1">
-        <v>86</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C91" s="1">
-        <v>87</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C92" s="1">
-        <v>88</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C93" s="1">
-        <v>89</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E93" s="1">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C94" s="1">
-        <v>90</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E94" s="1">
-        <v>10000158</v>
-      </c>
-    </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C95" s="1">
-        <v>91</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E95" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C96" s="1">
-        <v>92</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C97" s="1">
-        <v>93</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E97" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C98" s="1">
-        <v>94</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" s="1">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C99" s="1">
-        <v>95</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E99" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C100" s="1">
-        <v>96</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C101" s="1">
-        <v>97</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C102" s="1">
-        <v>98</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E102" s="1">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C103" s="1">
-        <v>99</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E103" s="1">
-        <v>61300001</v>
-      </c>
-    </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C104" s="1">
-        <v>100</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C105" s="1">
-        <v>101</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C106" s="1">
-        <v>102</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C107" s="1">
-        <v>103</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E107" s="1">
-        <v>70000001</v>
-      </c>
-    </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C108" s="1">
-        <v>104</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E108" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C109" s="1">
-        <v>105</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E109" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C110" s="1">
-        <v>106</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E110" s="1">
-        <v>80000001</v>
-      </c>
-    </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C111" s="1">
-        <v>107</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C112" s="1">
-        <v>108</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E112" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C113" s="1">
-        <v>109</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C114" s="1">
-        <v>110</v>
+      <c r="C114" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C115" s="1">
-        <v>111</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C116" s="1">
-        <v>112</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C117" s="1">
+    </row>
+    <row r="115" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B115" s="1">
         <v>113</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E117" s="1">
+      <c r="C115" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D115" s="1">
         <v>198</v>
       </c>
     </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C118" s="1">
+    <row r="116" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B116" s="1">
         <v>114</v>
       </c>
+      <c r="C116" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" s="1">
+        <v>90000001</v>
+      </c>
+    </row>
+    <row r="117" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B117" s="1">
+        <v>115</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D117" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="118" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B118" s="1">
+        <v>116</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="D118" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E118" s="1">
-        <v>90000001</v>
-      </c>
-    </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C119" s="1">
-        <v>115</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E119" s="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="119" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B119" s="1">
+        <v>117</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D119" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B120" s="1">
+        <v>118</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D120" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="121" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B121" s="1">
+        <v>119</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D121" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="122" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B122" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C120" s="1">
-        <v>116</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C121" s="1">
-        <v>117</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E121" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C122" s="1">
-        <v>118</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E122" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C123" s="1">
-        <v>119</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E123" s="1">
+      <c r="C122" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D122" s="1">
+        <v>20000001</v>
+      </c>
+    </row>
+    <row r="123" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B123" s="1">
+        <v>121</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D123" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B124" s="1">
+        <v>122</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D124" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="125" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B125" s="1">
+        <v>123</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D125" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="1">
+        <v>124</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D126" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="1">
+        <v>125</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="1">
+        <v>126</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D128" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="1">
+        <v>127</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="1">
+        <v>128</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D130" s="1">
+        <v>1000022</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="1">
+        <v>129</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D131" s="1">
+        <v>61600001</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="1">
+        <v>130</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D132" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" s="1">
+        <v>131</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D133" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="124" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C124" s="1">
-        <v>120</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E124" s="1">
-        <v>20000001</v>
-      </c>
-    </row>
-    <row r="125" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C125" s="1">
-        <v>121</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E125" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C126" s="1">
-        <v>122</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E126" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="127" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C127" s="1">
-        <v>123</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E127" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="128" spans="3:5">
-      <c r="C128" s="1">
-        <v>124</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E128" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="129" spans="3:5">
-      <c r="C129" s="1">
-        <v>125</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E129" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="3:5">
-      <c r="C130" s="1">
-        <v>126</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E130" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="3:5">
-      <c r="C131" s="1">
-        <v>127</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="132" spans="3:5">
-      <c r="C132" s="1">
-        <v>128</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E132" s="1">
-        <v>1000022</v>
-      </c>
-    </row>
-    <row r="133" spans="3:5">
-      <c r="C133" s="1">
-        <v>129</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E133" s="1">
-        <v>61600001</v>
-      </c>
-    </row>
-    <row r="134" spans="3:5">
-      <c r="C134" s="1">
-        <v>130</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E134" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" spans="3:5">
-      <c r="C135" s="1">
-        <v>131</v>
+    <row r="134" spans="2:4">
+      <c r="B134" s="1">
+        <v>132</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D134" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" s="1">
+        <v>133</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E135" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136" spans="3:5">
-      <c r="C136" s="1">
-        <v>132</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" s="1">
+        <v>134</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E136" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="137" spans="3:5">
-      <c r="C137" s="1">
-        <v>133</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" s="1">
+        <v>135</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="138" spans="3:5">
-      <c r="C138" s="1">
-        <v>134</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="139" spans="3:5">
-      <c r="C139" s="1">
-        <v>135</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" s="1">
+        <v>136</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D138" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="1">
+        <v>137</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="140" spans="3:5">
-      <c r="C140" s="1">
-        <v>136</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E140" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="141" spans="3:5">
-      <c r="C141" s="1">
-        <v>137</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="1">
+        <v>138</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D140" s="1">
+        <v>61700001</v>
+      </c>
+    </row>
+    <row r="141" ht="20.1" customHeight="1" spans="2:4">
+      <c r="B141" s="1">
+        <v>139</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="142" spans="3:5">
-      <c r="C142" s="1">
-        <v>138</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E142" s="1">
-        <v>61700001</v>
-      </c>
-    </row>
-    <row r="143" ht="20.1" customHeight="1" spans="3:5">
-      <c r="C143" s="1">
-        <v>139</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E115" r:id="rId3" display="1000001;100@601800051"/>
+    <hyperlink ref="D113" r:id="rId3" display="1000001;100@601800051"/>
   </hyperlinks>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
